--- a/corpus/xlsx/level-044/template.xlsx
+++ b/corpus/xlsx/level-044/template.xlsx
@@ -111,7 +111,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -152,14 +160,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -185,7 +185,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -201,15 +209,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">u</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">st</t>
+      <t xml:space="preserve">us</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">t</t>
     </r>
     <r>
       <rPr>
@@ -241,15 +249,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">r</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">r}</t>
     </r>
   </si>
   <si>
@@ -267,7 +267,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -308,14 +316,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -341,7 +341,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -390,14 +398,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">d</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -423,7 +423,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -479,15 +487,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">d</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">d}</t>
     </r>
   </si>
   <si>
@@ -505,7 +505,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -561,15 +569,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">l</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">l}</t>
     </r>
   </si>
   <si>
@@ -713,7 +713,7 @@
     <xdr:ext cx="914400" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1" descr="{{image:red}}"/>
+        <xdr:cNvPr id="1" name="Picture 1" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -744,7 +744,7 @@
     <xdr:ext cx="960120" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="2" name="Picture 2" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -775,7 +775,7 @@
     <xdr:ext cx="1005840" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3" descr="{{image:red}}"/>
+        <xdr:cNvPr id="3" name="Picture 3" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -806,7 +806,7 @@
     <xdr:ext cx="1051560" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="4" name="Picture 4" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -837,7 +837,7 @@
     <xdr:ext cx="1097280" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 5" descr="{{image:red}}"/>
+        <xdr:cNvPr id="5" name="Picture 5" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -868,7 +868,7 @@
     <xdr:ext cx="1143000" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 6" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="6" name="Picture 6" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -899,7 +899,7 @@
     <xdr:ext cx="1188720" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 7" descr="{{image:red}}"/>
+        <xdr:cNvPr id="7" name="Picture 7" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -930,7 +930,7 @@
     <xdr:ext cx="1234440" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 8" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="8" name="Picture 8" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -961,7 +961,7 @@
     <xdr:ext cx="1280160" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 9" descr="{{image:red}}"/>
+        <xdr:cNvPr id="9" name="Picture 9" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -992,7 +992,7 @@
     <xdr:ext cx="1325880" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 10" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="10" name="Picture 10" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
